--- a/public/assets/experiences.xlsx
+++ b/public/assets/experiences.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,9 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Title</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Position</t>
   </si>
   <si>
     <t>Description</t>
@@ -22,39 +28,68 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Trilogic - Support for Teaching and Learning Programming Logic (Academic Project)</t>
+    <t>Target IT</t>
+  </si>
+  <si>
+    <t>Lavavel, ReactJS, Azure, API, Webservices, Postman</t>
+  </si>
+  <si>
+    <t>Software Developer</t>
+  </si>
+  <si>
+    <t>Act as a Software Developer, contributing to bug resolution and feature development across the company's platforms (ReactJS and Laravel).</t>
+  </si>
+  <si>
+    <t>December, 2025 - Present</t>
+  </si>
+  <si>
+    <t>Diário Escola</t>
+  </si>
+  <si>
+    <t>HTML, CSS, JavaScript, PHP, Java, Objective C, SCRUM, Miro, API, Postman, Swagger, Confluence, Jira</t>
+  </si>
+  <si>
+    <t>Junior Software Developer</t>
+  </si>
+  <si>
+    <t>Act as a Junior Software Developer, contributing to bug resolution and feature development across Web (HTML, CSS, JavaScript, PHP), Android (Java), and iOS (Objective-C) platforms. Responsible for building responsive user interfaces and integrating REST APIs. Participated in SCRUM ceremonies focused on requirements analysis and task planning. Spearheaded the development of an integration project, collaborating on the architecture of a new solution with redesigned flows, updated business rules, new database structures (fields and tables), and API specifications. Used Miro for system mapping and documentation. Support the project through its implementation, bug resolution, and client assistance.</t>
+  </si>
+  <si>
+    <t>June, 2023 - November, 2025</t>
+  </si>
+  <si>
+    <t>Logimix (Academic Project)</t>
+  </si>
+  <si>
+    <t>Canva, Google Sheets</t>
+  </si>
+  <si>
+    <t>Junior Project Manager</t>
+  </si>
+  <si>
+    <t>Plan and deliver robotics workshops in local schools and surrounding communities. Create visual and written content for social media and manage project outreach. Document workshop stages and activities for internal and external reporting. Collaborate with the team to promote the development of computational thinking through educational robotics.</t>
+  </si>
+  <si>
+    <t>January, 2022 - December, 2022</t>
+  </si>
+  <si>
+    <t>Trilogic (Academic Project)</t>
+  </si>
+  <si>
+    <t>Canva, WordPress, Google Sheets</t>
   </si>
   <si>
     <t>Organize and lead tasks and team meetings. Test and evaluate the educational platform. Design a new visual identity and user experience for the web platform. Deliver programming logic workshops to high school students. Maintain and update the project’s website using WordPress. Manage the project’s social media to share updates and engage with the audience.</t>
   </si>
   <si>
-    <t>Jan, 2021 - Dec, 2021</t>
-  </si>
-  <si>
-    <t>Logimix - Educational Robotics Workshops in Professional Education: The Development of Computational Thinking as an Aid to Programming Logic (Academic Project)</t>
-  </si>
-  <si>
-    <t>Plan and deliver robotics workshops in local schools and surrounding communities. Create visual and written content for social media and manage project outreach. Document workshop stages and activities for internal and external reporting. Collaborate with the team to promote the development of computational thinking through educational robotics.</t>
-  </si>
-  <si>
-    <t>Jan, 2022 - Dec, 2022</t>
-  </si>
-  <si>
-    <t>Junior Software Developer</t>
-  </si>
-  <si>
-    <t>Act as a Junior Software Developer, contributing to bug resolution and feature development across Web (HTML, CSS, JavaScript, PHP), Android (Java), and iOS (Objective-C) platforms. Responsible for building responsive user interfaces and integrating REST APIs. Participate in SCRUM ceremonies focused on requirements analysis and task planning.
-Currently leading the development of an integration project, collaborating on the architecture of a new solution with redesigned flows, updated business rules, new database structures (fields and tables), and API specifications. Use Miro for system mapping and documentation. Support the project through its implementation, bug resolution, and client assistance.</t>
-  </si>
-  <si>
-    <t>Jun, 2023 - Present</t>
+    <t>January, 2021 - December, 2021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -72,6 +107,10 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -87,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -96,6 +135,15 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -107,6 +155,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -309,6 +361,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="2" width="30.13"/>
+    <col customWidth="1" min="3" max="3" width="27.75"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -320,38 +376,79 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/experiences.xlsx
+++ b/public/assets/experiences.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Company</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Software Developer</t>
   </si>
   <si>
-    <t>Act as a Software Developer, contributing to bug resolution and feature development across the company's platforms (ReactJS and Laravel).</t>
+    <t>Built scalable fiscal and financial web apps using Laravel and ReactJS. Designed and integrated REST APIs and Webservices with external ERPs. Implemented complex business logic for supplier portals and enterprise solutions.</t>
   </si>
   <si>
     <t>December, 2025 - Present</t>
@@ -52,37 +52,10 @@
     <t>Junior Software Developer</t>
   </si>
   <si>
-    <t>Act as a Junior Software Developer, contributing to bug resolution and feature development across Web (HTML, CSS, JavaScript, PHP), Android (Java), and iOS (Objective-C) platforms. Responsible for building responsive user interfaces and integrating REST APIs. Participated in SCRUM ceremonies focused on requirements analysis and task planning. Spearheaded the development of an integration project, collaborating on the architecture of a new solution with redesigned flows, updated business rules, new database structures (fields and tables), and API specifications. Used Miro for system mapping and documentation. Support the project through its implementation, bug resolution, and client assistance.</t>
+    <t>Developed and maintained Web, Android (Java), and iOS (Objective-C) applications. Built responsive layouts and consumed REST APIs. Defined architecture, database modeling, and business rules for integration projects. Mapped processes and created technical documentation using Miro. Analyzed requirements and planned tasks in a SCRUM environment. Provided technical support for implementation and client assistance.</t>
   </si>
   <si>
     <t>June, 2023 - November, 2025</t>
-  </si>
-  <si>
-    <t>Logimix (Academic Project)</t>
-  </si>
-  <si>
-    <t>Canva, Google Sheets</t>
-  </si>
-  <si>
-    <t>Junior Project Manager</t>
-  </si>
-  <si>
-    <t>Plan and deliver robotics workshops in local schools and surrounding communities. Create visual and written content for social media and manage project outreach. Document workshop stages and activities for internal and external reporting. Collaborate with the team to promote the development of computational thinking through educational robotics.</t>
-  </si>
-  <si>
-    <t>January, 2022 - December, 2022</t>
-  </si>
-  <si>
-    <t>Trilogic (Academic Project)</t>
-  </si>
-  <si>
-    <t>Canva, WordPress, Google Sheets</t>
-  </si>
-  <si>
-    <t>Organize and lead tasks and team meetings. Test and evaluate the educational platform. Design a new visual identity and user experience for the web platform. Deliver programming logic workshops to high school students. Maintain and update the project’s website using WordPress. Manage the project’s social media to share updates and engage with the audience.</t>
-  </si>
-  <si>
-    <t>January, 2021 - December, 2021</t>
   </si>
 </sst>
 </file>
@@ -126,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -141,9 +114,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -417,40 +387,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
